--- a/artfynd/A 48650-2021 artfynd.xlsx
+++ b/artfynd/A 48650-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48650-2021 artfynd.xlsx
+++ b/artfynd/A 48650-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113149825</v>
+        <v>113149954</v>
       </c>
       <c r="B2" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662835</v>
+        <v>662790</v>
       </c>
       <c r="R2" t="n">
-        <v>7277600</v>
+        <v>7277540</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,12 +783,7 @@
         <v>113149828</v>
       </c>
       <c r="B3" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,12 +800,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -895,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113150008</v>
+        <v>113149922</v>
       </c>
       <c r="B4" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662835</v>
+        <v>662790</v>
       </c>
       <c r="R4" t="n">
-        <v>7277520</v>
+        <v>7277555</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,43 +990,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113150086</v>
+        <v>113149825</v>
       </c>
       <c r="B5" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662840</v>
+        <v>662835</v>
       </c>
       <c r="R5" t="n">
-        <v>7277475</v>
+        <v>7277600</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113150020</v>
+        <v>113150008</v>
       </c>
       <c r="B6" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,27 +1106,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1162,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662840</v>
+        <v>662835</v>
       </c>
       <c r="R6" t="n">
-        <v>7277475</v>
+        <v>7277520</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,43 +1200,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113150091</v>
+        <v>113149926</v>
       </c>
       <c r="B7" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1272,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662840</v>
+        <v>662790</v>
       </c>
       <c r="R7" t="n">
-        <v>7277475</v>
+        <v>7277555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,6 +1302,431 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113150091</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fiskträskberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>662840</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7277475</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113149820</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fiskträskberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>662840</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7277615</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på flera gamla sälgar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113150020</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fiskträskberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>662840</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7277475</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113150086</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fiskträskberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>662840</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7277475</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48650-2021 artfynd.xlsx
+++ b/artfynd/A 48650-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113149954</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113149828</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113149922</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113149825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113150008</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113149926</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113150091</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113149820</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113150020</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,8 +1777,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113150086</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>